--- a/dados/rubricas_consultoria_preenchida e Validada.xlsx
+++ b/dados/rubricas_consultoria_preenchida e Validada.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projetos\RubricasEsocial\dados\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E372FC4-14C3-4926-980D-131065E0F120}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADA0C2D6-CF4D-4642-BB77-700711EA0823}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$Q$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$100</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="279">
   <si>
     <t>codigo</t>
   </si>
@@ -195,9 +195,6 @@
   </si>
   <si>
     <t>Valor relativo ao nascimento do filho de servidor público, previsto em lei</t>
-  </si>
-  <si>
-    <t>09 - Outras verbas não consideradas como base de cálculo ou rendimento tributável</t>
   </si>
   <si>
     <t>Abono permanência</t>
@@ -540,9 +537,6 @@
     <t>Art. 28,III da Lei n° 8.212/91</t>
   </si>
   <si>
-    <t>09 - Outras verbas não consideradas como base de cálculo ou rendimento</t>
-  </si>
-  <si>
     <t>Retiradas (pró-labore) de diretores não empregados</t>
   </si>
   <si>
@@ -875,6 +869,12 @@
   </si>
   <si>
     <t>AJUSTE_API</t>
+  </si>
+  <si>
+    <t>exige_analise_irrf</t>
+  </si>
+  <si>
+    <t>67 - Plano privado coletivo de assistência à saúde</t>
   </si>
 </sst>
 </file>
@@ -916,9 +916,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1221,7 +1224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q100"/>
+  <dimension ref="A1:R100"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.33203125" style="1" bestFit="1" customWidth="1"/>
@@ -1241,10 +1244,11 @@
     <col min="15" max="15" width="27.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="1"/>
+    <col min="18" max="18" width="18.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1294,10 +1298,13 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>274</v>
+      </c>
+      <c r="R1" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -1323,7 +1330,7 @@
         <v>19</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>22</v>
@@ -1338,13 +1345,16 @@
         <v>24</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q2" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1012</v>
       </c>
@@ -1385,13 +1395,16 @@
         <v>24</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1015</v>
       </c>
@@ -1432,13 +1445,16 @@
         <v>35</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q4" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1016</v>
       </c>
@@ -1479,13 +1495,16 @@
         <v>24</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>1017</v>
       </c>
@@ -1529,13 +1548,16 @@
         <v>24</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q6" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R6" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>1018</v>
       </c>
@@ -1579,13 +1601,16 @@
         <v>24</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q7" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>1019</v>
       </c>
@@ -1629,13 +1654,16 @@
         <v>24</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q8" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>1216</v>
       </c>
@@ -1676,13 +1704,16 @@
         <v>24</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q9" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>1217</v>
       </c>
@@ -1723,13 +1754,16 @@
         <v>24</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q10" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>1411</v>
       </c>
@@ -1758,7 +1792,7 @@
         <v>19</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L11" s="1" t="s">
         <v>30</v>
@@ -1773,24 +1807,27 @@
         <v>24</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q11" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>1412</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>19</v>
@@ -1805,7 +1842,7 @@
         <v>19</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L12" s="1" t="s">
         <v>30</v>
@@ -1820,24 +1857,27 @@
         <v>24</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q12" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>1619</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>58</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>19</v>
@@ -1852,7 +1892,7 @@
         <v>19</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L13" s="1" t="s">
         <v>30</v>
@@ -1867,45 +1907,48 @@
         <v>24</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q13" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>1651</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="G14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L14" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="M14" s="1" t="s">
         <v>19</v>
@@ -1917,27 +1960,30 @@
         <v>35</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q14" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R14" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>1652</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>27</v>
@@ -1967,24 +2013,27 @@
         <v>24</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q15" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R15" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>1799</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>40</v>
@@ -2002,7 +2051,7 @@
         <v>19</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L16" s="1" t="s">
         <v>30</v>
@@ -2017,24 +2066,27 @@
         <v>24</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q16" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>1800</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>40</v>
@@ -2067,24 +2119,27 @@
         <v>24</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q17" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R17" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>1806</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>40</v>
@@ -2096,13 +2151,13 @@
         <v>20</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J18" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L18" s="1" t="s">
         <v>30</v>
@@ -2117,24 +2172,27 @@
         <v>35</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q18" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R18" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>1807</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>40</v>
@@ -2167,24 +2225,27 @@
         <v>24</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q19" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>1808</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>40</v>
@@ -2196,13 +2257,13 @@
         <v>20</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L20" s="1" t="s">
         <v>30</v>
@@ -2217,24 +2278,27 @@
         <v>35</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q20" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>1809</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>40</v>
@@ -2267,24 +2331,27 @@
         <v>24</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q21" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>1811</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>40</v>
@@ -2317,24 +2384,27 @@
         <v>24</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q22" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>1899</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G23" s="1" t="s">
         <v>27</v>
@@ -2364,24 +2434,27 @@
         <v>24</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q23" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R23" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>1901</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G24" s="1" t="s">
         <v>27</v>
@@ -2411,24 +2484,27 @@
         <v>24</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q24" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>2801</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>27</v>
@@ -2458,24 +2534,27 @@
         <v>24</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q25" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>2903</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>27</v>
@@ -2505,24 +2584,27 @@
         <v>24</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q26" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R26" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>3510</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>27</v>
@@ -2552,24 +2634,27 @@
         <v>24</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q27" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R27" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>3511</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G28" s="1" t="s">
         <v>27</v>
@@ -2599,24 +2684,27 @@
         <v>24</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q28" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R28" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>4011</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G29" s="1" t="s">
         <v>27</v>
@@ -2646,24 +2734,27 @@
         <v>24</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q29" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R29" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>6108</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>27</v>
@@ -2693,24 +2784,27 @@
         <v>24</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q30" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>6119</v>
       </c>
       <c r="B31" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E31" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>98</v>
       </c>
       <c r="G31" s="1" t="s">
         <v>19</v>
@@ -2725,7 +2819,7 @@
         <v>19</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>30</v>
@@ -2740,24 +2834,27 @@
         <v>24</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q31" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>7006</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G32" s="1" t="s">
         <v>19</v>
@@ -2772,7 +2869,7 @@
         <v>19</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L32" s="1" t="s">
         <v>30</v>
@@ -2787,24 +2884,27 @@
         <v>24</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q32" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>7007</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>19</v>
@@ -2834,24 +2934,27 @@
         <v>24</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q33" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>7008</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>19</v>
@@ -2881,24 +2984,27 @@
         <v>24</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q34" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>9202</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>19</v>
@@ -2913,7 +3019,7 @@
         <v>19</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L35" s="1" t="s">
         <v>30</v>
@@ -2928,24 +3034,27 @@
         <v>24</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q35" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>9205</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>19</v>
@@ -2960,7 +3069,7 @@
         <v>19</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L36" s="1" t="s">
         <v>30</v>
@@ -2975,24 +3084,27 @@
         <v>24</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q36" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>9207</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>19</v>
@@ -3007,7 +3119,7 @@
         <v>19</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L37" s="1" t="s">
         <v>30</v>
@@ -3022,24 +3134,27 @@
         <v>24</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q37" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="38" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>9208</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>19</v>
@@ -3054,7 +3169,7 @@
         <v>19</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L38" s="1" t="s">
         <v>30</v>
@@ -3069,24 +3184,27 @@
         <v>24</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q38" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="39" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>9211</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>19</v>
@@ -3101,7 +3219,7 @@
         <v>19</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L39" s="1" t="s">
         <v>30</v>
@@ -3116,24 +3234,27 @@
         <v>24</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q39" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>9212</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G40" s="1" t="s">
         <v>19</v>
@@ -3148,7 +3269,7 @@
         <v>19</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L40" s="1" t="s">
         <v>30</v>
@@ -3163,24 +3284,27 @@
         <v>24</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q40" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="41" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>9218</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>19</v>
@@ -3195,7 +3319,7 @@
         <v>19</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L41" s="1" t="s">
         <v>30</v>
@@ -3210,24 +3334,27 @@
         <v>24</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q41" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="42" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>9240</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>19</v>
@@ -3242,7 +3369,7 @@
         <v>19</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L42" s="1" t="s">
         <v>30</v>
@@ -3257,24 +3384,27 @@
         <v>24</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q42" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="43" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>9241</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G43" s="1" t="s">
         <v>19</v>
@@ -3289,7 +3419,7 @@
         <v>19</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L43" s="1" t="s">
         <v>30</v>
@@ -3304,24 +3434,27 @@
         <v>24</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q43" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>9242</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>19</v>
@@ -3336,7 +3469,7 @@
         <v>19</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L44" s="1" t="s">
         <v>30</v>
@@ -3351,24 +3484,27 @@
         <v>24</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q44" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R44" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>9243</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>19</v>
@@ -3383,7 +3519,7 @@
         <v>19</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L45" s="1" t="s">
         <v>30</v>
@@ -3398,24 +3534,27 @@
         <v>24</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q45" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R45" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>9244</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G46" s="1" t="s">
         <v>19</v>
@@ -3430,7 +3569,7 @@
         <v>19</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L46" s="1" t="s">
         <v>30</v>
@@ -3445,24 +3584,27 @@
         <v>24</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q46" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R46" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>9253</v>
       </c>
       <c r="B47" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C47" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="E47" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>19</v>
@@ -3477,7 +3619,7 @@
         <v>19</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L47" s="1" t="s">
         <v>30</v>
@@ -3492,24 +3634,27 @@
         <v>24</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q47" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R47" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>9260</v>
       </c>
       <c r="B48" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C48" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="E48" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="G48" s="1" t="s">
         <v>19</v>
@@ -3524,7 +3669,7 @@
         <v>19</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L48" s="1" t="s">
         <v>30</v>
@@ -3539,24 +3684,27 @@
         <v>24</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q48" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R48" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>9291</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G49" s="1" t="s">
         <v>19</v>
@@ -3571,7 +3719,7 @@
         <v>19</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L49" s="1" t="s">
         <v>30</v>
@@ -3586,24 +3734,27 @@
         <v>24</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q49" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R49" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>9292</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>19</v>
@@ -3618,7 +3769,7 @@
         <v>19</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L50" s="1" t="s">
         <v>30</v>
@@ -3633,24 +3784,27 @@
         <v>24</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q50" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R50" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>9293</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G51" s="1" t="s">
         <v>19</v>
@@ -3665,7 +3819,7 @@
         <v>19</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L51" s="1" t="s">
         <v>30</v>
@@ -3680,24 +3834,27 @@
         <v>24</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q51" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>9294</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G52" s="1" t="s">
         <v>19</v>
@@ -3712,7 +3869,7 @@
         <v>19</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L52" s="1" t="s">
         <v>30</v>
@@ -3727,24 +3884,27 @@
         <v>24</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q52" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>9907</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G53" s="1" t="s">
         <v>19</v>
@@ -3759,7 +3919,7 @@
         <v>19</v>
       </c>
       <c r="K53" s="1" t="s">
-        <v>53</v>
+        <v>20</v>
       </c>
       <c r="L53" s="1" t="s">
         <v>30</v>
@@ -3774,24 +3934,27 @@
         <v>24</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q53" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R53" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>9912</v>
       </c>
       <c r="B54" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>145</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>146</v>
       </c>
       <c r="G54" s="1" t="s">
         <v>19</v>
@@ -3806,7 +3969,7 @@
         <v>19</v>
       </c>
       <c r="K54" s="1" t="s">
-        <v>53</v>
+        <v>278</v>
       </c>
       <c r="L54" s="1" t="s">
         <v>30</v>
@@ -3821,24 +3984,27 @@
         <v>24</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q54" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>275</v>
+      </c>
+      <c r="R54" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>1009</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C55" s="1">
         <v>1012014</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G55" s="1" t="s">
         <v>27</v>
@@ -3847,10 +4013,10 @@
         <v>28</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J55" s="1" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="K55" s="1" t="s">
         <v>29</v>
@@ -3862,19 +4028,22 @@
         <v>27</v>
       </c>
       <c r="N55" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O55" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="O55" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="P55" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q55" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>1020</v>
       </c>
@@ -3888,7 +4057,7 @@
         <v>30042023</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G56" s="1" t="s">
         <v>27</v>
@@ -3897,7 +4066,7 @@
         <v>28</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>27</v>
@@ -3906,30 +4075,33 @@
         <v>34</v>
       </c>
       <c r="L56" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M56" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N56" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O56" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M56" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N56" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="O56" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P56" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q56" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R56" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>1604</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C57" s="1">
         <v>1052018</v>
@@ -3938,26 +4110,26 @@
         <v>31032019</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I57" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J57" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I57" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J57" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K57" s="1" t="s">
+      <c r="L57" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="L57" s="1" t="s">
-        <v>160</v>
-      </c>
       <c r="M57" s="1" t="s">
         <v>19</v>
       </c>
@@ -3965,21 +4137,24 @@
         <v>23</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q57" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R57" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>2501</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C58" s="1">
         <v>1012014</v>
@@ -3988,7 +4163,7 @@
         <v>30042018</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G58" s="1" t="s">
         <v>19</v>
@@ -3997,7 +4172,7 @@
         <v>20</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>27</v>
@@ -4006,7 +4181,7 @@
         <v>29</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="M58" s="1" t="s">
         <v>19</v>
@@ -4015,74 +4190,80 @@
         <v>23</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q58" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R58" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>2999</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C59" s="1">
         <v>1012014</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="G59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I59" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I59" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="J59" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L59" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M59" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N59" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O59" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M59" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N59" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O59" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P59" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q59" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R59" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>3506</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C60" s="1">
         <v>1012014</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>27</v>
@@ -4091,7 +4272,7 @@
         <v>28</v>
       </c>
       <c r="I60" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J60" s="1" t="s">
         <v>27</v>
@@ -4100,7 +4281,7 @@
         <v>29</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M60" s="1" t="s">
         <v>19</v>
@@ -4109,27 +4290,30 @@
         <v>23</v>
       </c>
       <c r="O60" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q60" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R60" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>3509</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C61" s="1">
         <v>1012014</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>27</v>
@@ -4138,7 +4322,7 @@
         <v>28</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J61" s="1" t="s">
         <v>27</v>
@@ -4147,36 +4331,39 @@
         <v>29</v>
       </c>
       <c r="L61" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M61" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O61" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M61" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P61" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q61" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R61" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>3520</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C62" s="1">
         <v>1012014</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>27</v>
@@ -4185,7 +4372,7 @@
         <v>28</v>
       </c>
       <c r="I62" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J62" s="1" t="s">
         <v>27</v>
@@ -4194,36 +4381,39 @@
         <v>29</v>
       </c>
       <c r="L62" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M62" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O62" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M62" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N62" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O62" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P62" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q62" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R62" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>3525</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C63" s="1">
         <v>1052018</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>19</v>
@@ -4232,7 +4422,7 @@
         <v>20</v>
       </c>
       <c r="I63" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="J63" s="1" t="s">
         <v>27</v>
@@ -4241,36 +4431,39 @@
         <v>29</v>
       </c>
       <c r="L63" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M63" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N63" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O63" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M63" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N63" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O63" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P63" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q63" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R63" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>6901</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C64" s="1">
         <v>1012014</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>19</v>
@@ -4279,16 +4472,16 @@
         <v>20</v>
       </c>
       <c r="I64" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J64" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K64" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M64" s="1" t="s">
         <v>19</v>
@@ -4297,27 +4490,30 @@
         <v>23</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P64" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q64" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R64" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>9209</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C65" s="1">
         <v>1012014</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>27</v>
@@ -4326,7 +4522,7 @@
         <v>28</v>
       </c>
       <c r="I65" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J65" s="1" t="s">
         <v>27</v>
@@ -4335,36 +4531,39 @@
         <v>29</v>
       </c>
       <c r="L65" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M65" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N65" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q65" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R65" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>9210</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C66" s="1">
         <v>1012014</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G66" s="1" t="s">
         <v>27</v>
@@ -4373,7 +4572,7 @@
         <v>28</v>
       </c>
       <c r="I66" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="J66" s="1" t="s">
         <v>27</v>
@@ -4382,83 +4581,89 @@
         <v>29</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="M66" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N66" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q66" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R66" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>9214</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C67" s="1">
         <v>1012014</v>
       </c>
       <c r="E67" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J67" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L67" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N67" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="G67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I67" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J67" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L67" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="M67" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N67" s="1" t="s">
-        <v>190</v>
-      </c>
       <c r="O67" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q67" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="68" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R67" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>9221</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C68" s="1">
         <v>1012014</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>19</v>
@@ -4467,16 +4672,16 @@
         <v>20</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K68" s="1" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M68" s="1" t="s">
         <v>19</v>
@@ -4485,21 +4690,24 @@
         <v>23</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q68" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="69" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R68" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>9290</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C69" s="1">
         <v>1012014</v>
@@ -4508,7 +4716,7 @@
         <v>31072021</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G69" s="1" t="s">
         <v>19</v>
@@ -4517,17 +4725,17 @@
         <v>20</v>
       </c>
       <c r="I69" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J69" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K69" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L69" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L69" s="1" t="s">
-        <v>155</v>
-      </c>
       <c r="M69" s="1" t="s">
         <v>19</v>
       </c>
@@ -4535,74 +4743,80 @@
         <v>23</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q69" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="70" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R69" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>9931</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C70" s="1">
         <v>1012014</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I70" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J70" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K70" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L70" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="G70" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H70" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="I70" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="J70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K70" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L70" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="M70" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N70" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q70" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="71" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R70" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>1022</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C71" s="1">
         <v>1012014</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>19</v>
@@ -4611,16 +4825,16 @@
         <v>20</v>
       </c>
       <c r="I71" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J71" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K71" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>19</v>
@@ -4629,27 +4843,30 @@
         <v>23</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q71" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="72" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R71" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>1404</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C72" s="1">
         <v>1012014</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="G72" s="1" t="s">
         <v>19</v>
@@ -4658,16 +4875,16 @@
         <v>20</v>
       </c>
       <c r="I72" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J72" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K72" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="M72" s="1" t="s">
         <v>19</v>
@@ -4676,27 +4893,30 @@
         <v>23</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q72" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="73" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R72" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>1405</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C73" s="1">
         <v>1012014</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="G73" s="1" t="s">
         <v>19</v>
@@ -4705,16 +4925,16 @@
         <v>20</v>
       </c>
       <c r="I73" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J73" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K73" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>19</v>
@@ -4723,74 +4943,80 @@
         <v>23</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q73" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="74" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R73" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>1407</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="C74" s="1">
         <v>1012014</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O74" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="G74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I74" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K74" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L74" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="M74" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N74" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O74" s="1" t="s">
-        <v>212</v>
-      </c>
       <c r="P74" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q74" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="75" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R74" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>1601</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C75" s="1">
         <v>1012014</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="G75" s="1" t="s">
         <v>19</v>
@@ -4799,16 +5025,16 @@
         <v>20</v>
       </c>
       <c r="I75" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J75" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K75" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L75" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="M75" s="1" t="s">
         <v>19</v>
@@ -4817,27 +5043,30 @@
         <v>23</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="P75" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q75" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="76" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R75" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>1623</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C76" s="1">
         <v>1012014</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="G76" s="1" t="s">
         <v>19</v>
@@ -4846,16 +5075,16 @@
         <v>20</v>
       </c>
       <c r="I76" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J76" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K76" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>19</v>
@@ -4864,27 +5093,30 @@
         <v>23</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P76" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q76" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="77" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R76" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>1629</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C77" s="1">
         <v>1012014</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G77" s="1" t="s">
         <v>19</v>
@@ -4893,16 +5125,16 @@
         <v>20</v>
       </c>
       <c r="I77" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J77" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K77" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L77" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="M77" s="1" t="s">
         <v>19</v>
@@ -4911,27 +5143,30 @@
         <v>23</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P77" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q77" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="78" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R77" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>1650</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C78" s="1">
         <v>1052018</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G78" s="1" t="s">
         <v>19</v>
@@ -4940,16 +5175,16 @@
         <v>20</v>
       </c>
       <c r="I78" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J78" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K78" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="M78" s="1" t="s">
         <v>19</v>
@@ -4958,27 +5193,30 @@
         <v>23</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P78" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q78" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="79" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R78" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>1805</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C79" s="1">
         <v>1012014</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G79" s="1" t="s">
         <v>27</v>
@@ -4987,7 +5225,7 @@
         <v>28</v>
       </c>
       <c r="I79" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J79" s="1" t="s">
         <v>27</v>
@@ -4996,36 +5234,39 @@
         <v>29</v>
       </c>
       <c r="L79" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="M79" s="1" t="s">
         <v>27</v>
       </c>
       <c r="N79" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="O79" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="O79" s="1" t="s">
-        <v>151</v>
-      </c>
       <c r="P79" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q79" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="80" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>2901</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C80" s="1">
         <v>1012014</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="G80" s="1" t="s">
         <v>19</v>
@@ -5034,39 +5275,42 @@
         <v>20</v>
       </c>
       <c r="I80" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="J80" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K80" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L80" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="M80" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N80" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O80" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M80" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N80" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O80" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P80" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q80" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R80" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>2902</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C81" s="1">
         <v>1012014</v>
@@ -5075,7 +5319,7 @@
         <v>31072021</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G81" s="1" t="s">
         <v>19</v>
@@ -5084,45 +5328,48 @@
         <v>20</v>
       </c>
       <c r="I81" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K81" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L81" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L81" s="1" t="s">
+      <c r="M81" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O81" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M81" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N81" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O81" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P81" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q81" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R81" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>2930</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C82" s="1">
         <v>1012014</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G82" s="1" t="s">
         <v>19</v>
@@ -5131,92 +5378,98 @@
         <v>20</v>
       </c>
       <c r="I82" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K82" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L82" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K82" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L82" s="1" t="s">
+      <c r="M82" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N82" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O82" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M82" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N82" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O82" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P82" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q82" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R82" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>5504</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="C83" s="1">
         <v>1012014</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L83" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="G83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I83" s="1" t="s">
+      <c r="M83" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="N83" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="J83" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K83" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L83" s="1" t="s">
+      <c r="O83" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="M83" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="N83" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="O83" s="1" t="s">
-        <v>236</v>
-      </c>
       <c r="P83" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q83" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="84" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R83" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>9200</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="C84" s="1">
         <v>1012014</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G84" s="1" t="s">
         <v>19</v>
@@ -5225,45 +5478,48 @@
         <v>20</v>
       </c>
       <c r="I84" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L84" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J84" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K84" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L84" s="1" t="s">
+      <c r="M84" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O84" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N84" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O84" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P84" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q84" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="85" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R84" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>9219</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>239</v>
-      </c>
-      <c r="C85" s="1">
+        <v>237</v>
+      </c>
+      <c r="C85" s="2">
         <v>1012014</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G85" s="1" t="s">
         <v>19</v>
@@ -5272,16 +5528,16 @@
         <v>20</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J85" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K85" s="1" t="s">
-        <v>167</v>
+        <v>278</v>
       </c>
       <c r="L85" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M85" s="1" t="s">
         <v>19</v>
@@ -5290,21 +5546,24 @@
         <v>23</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P85" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q85" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="86" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R85" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>9220</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C86" s="1">
         <v>1012014</v>
@@ -5313,7 +5572,7 @@
         <v>30062021</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G86" s="1" t="s">
         <v>19</v>
@@ -5322,16 +5581,16 @@
         <v>20</v>
       </c>
       <c r="I86" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J86" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K86" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L86" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>19</v>
@@ -5340,27 +5599,30 @@
         <v>23</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P86" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q86" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="87" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R86" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>9226</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="C87" s="1">
         <v>1012014</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="G87" s="1" t="s">
         <v>19</v>
@@ -5369,16 +5631,16 @@
         <v>20</v>
       </c>
       <c r="I87" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J87" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K87" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L87" s="1" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="M87" s="1" t="s">
         <v>19</v>
@@ -5387,27 +5649,30 @@
         <v>23</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q87" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="88" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>9230</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C88" s="1">
         <v>1012014</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G88" s="1" t="s">
         <v>19</v>
@@ -5416,16 +5681,16 @@
         <v>20</v>
       </c>
       <c r="I88" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J88" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K88" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L88" s="1" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>19</v>
@@ -5434,27 +5699,30 @@
         <v>23</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q88" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="89" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R88" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>9231</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="C89" s="1">
         <v>1012014</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="G89" s="1" t="s">
         <v>19</v>
@@ -5463,16 +5731,16 @@
         <v>20</v>
       </c>
       <c r="I89" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J89" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K89" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L89" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>19</v>
@@ -5481,27 +5749,30 @@
         <v>23</v>
       </c>
       <c r="O89" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P89" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q89" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="90" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R89" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>9232</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="C90" s="1">
         <v>1012014</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="G90" s="1" t="s">
         <v>19</v>
@@ -5510,16 +5781,16 @@
         <v>20</v>
       </c>
       <c r="I90" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J90" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K90" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>19</v>
@@ -5528,27 +5799,30 @@
         <v>23</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q90" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="91" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R90" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>9233</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C91" s="1">
         <v>1012014</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="G91" s="1" t="s">
         <v>19</v>
@@ -5557,16 +5831,16 @@
         <v>20</v>
       </c>
       <c r="I91" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J91" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>19</v>
@@ -5575,27 +5849,30 @@
         <v>23</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q91" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="92" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R91" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>9250</v>
       </c>
       <c r="B92" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C92" s="1">
         <v>1012014</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="G92" s="1" t="s">
         <v>19</v>
@@ -5604,16 +5881,16 @@
         <v>20</v>
       </c>
       <c r="I92" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J92" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K92" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L92" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M92" s="1" t="s">
         <v>19</v>
@@ -5622,27 +5899,30 @@
         <v>23</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q92" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="93" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R92" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>9270</v>
       </c>
       <c r="B93" s="1" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C93" s="1">
         <v>1012014</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>19</v>
@@ -5651,16 +5931,16 @@
         <v>20</v>
       </c>
       <c r="I93" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J93" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K93" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L93" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M93" s="1" t="s">
         <v>19</v>
@@ -5669,27 +5949,30 @@
         <v>23</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P93" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q93" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="94" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R93" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>9299</v>
       </c>
       <c r="B94" s="1" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C94" s="1">
         <v>1012014</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>19</v>
@@ -5698,45 +5981,48 @@
         <v>20</v>
       </c>
       <c r="I94" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K94" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L94" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J94" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K94" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L94" s="1" t="s">
+      <c r="M94" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N94" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O94" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M94" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N94" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O94" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P94" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q94" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="95" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R94" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>9902</v>
       </c>
       <c r="B95" s="1" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C95" s="1">
         <v>1012014</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="G95" s="1" t="s">
         <v>19</v>
@@ -5745,16 +6031,16 @@
         <v>20</v>
       </c>
       <c r="I95" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J95" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K95" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L95" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M95" s="1" t="s">
         <v>19</v>
@@ -5763,27 +6049,30 @@
         <v>23</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q95" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="96" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R95" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>9904</v>
       </c>
       <c r="B96" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C96" s="1">
         <v>1012014</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="G96" s="1" t="s">
         <v>19</v>
@@ -5792,16 +6081,16 @@
         <v>20</v>
       </c>
       <c r="I96" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J96" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K96" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L96" s="1" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="M96" s="1" t="s">
         <v>19</v>
@@ -5810,27 +6099,30 @@
         <v>23</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q96" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="97" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R96" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="97" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>9911</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C97" s="1">
         <v>1012014</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="G97" s="1" t="s">
         <v>19</v>
@@ -5839,39 +6131,42 @@
         <v>20</v>
       </c>
       <c r="I97" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="L97" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="J97" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K97" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="L97" s="1" t="s">
+      <c r="M97" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="O97" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M97" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="N97" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="O97" s="1" t="s">
-        <v>156</v>
-      </c>
       <c r="P97" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q97" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="98" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="98" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>9950</v>
       </c>
       <c r="B98" s="1" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C98" s="1">
         <v>1012014</v>
@@ -5880,7 +6175,7 @@
         <v>31102019</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G98" s="1" t="s">
         <v>19</v>
@@ -5889,16 +6184,16 @@
         <v>20</v>
       </c>
       <c r="I98" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J98" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K98" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="M98" s="1" t="s">
         <v>19</v>
@@ -5907,21 +6202,24 @@
         <v>23</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P98" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q98" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="99" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R98" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="99" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>9951</v>
       </c>
       <c r="B99" s="1" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="C99" s="1">
         <v>1012014</v>
@@ -5930,7 +6228,7 @@
         <v>31102019</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="G99" s="1" t="s">
         <v>19</v>
@@ -5939,16 +6237,16 @@
         <v>20</v>
       </c>
       <c r="I99" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J99" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K99" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="M99" s="1" t="s">
         <v>19</v>
@@ -5957,27 +6255,30 @@
         <v>23</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q99" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" ht="14.4" x14ac:dyDescent="0.3">
+        <v>276</v>
+      </c>
+      <c r="R99" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="100" spans="1:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>9989</v>
       </c>
       <c r="B100" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C100" s="1">
         <v>1012014</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G100" s="1" t="s">
         <v>19</v>
@@ -5986,16 +6287,16 @@
         <v>20</v>
       </c>
       <c r="I100" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J100" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K100" s="1" t="s">
-        <v>167</v>
+        <v>20</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="M100" s="1" t="s">
         <v>19</v>
@@ -6004,17 +6305,20 @@
         <v>23</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="Q100" t="s">
-        <v>278</v>
+        <v>276</v>
+      </c>
+      <c r="R100" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R100" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
